--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>402 Payment Required: "{"error":"Your balance is low, pls visit the dashboard to top up"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-22T00:17:42.102Z</v>
+        <v>2026-10-22T06:24:51.486Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>402 Payment Required: "{"error":"Your balance is low, pls visit the dashboard to top up"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-22T00:17:45.092Z</v>
+        <v>2026-10-22T06:24:54.439Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>402 Payment Required: "{"error":"Your balance is low, pls visit the dashboard to top up"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-22T06:24:51.486Z</v>
+        <v>2026-10-22T12:25:03.982Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>402 Payment Required: "{"error":"Your balance is low, pls visit the dashboard to top up"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-22T06:24:54.439Z</v>
+        <v>2026-10-22T12:25:07.109Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>402 Payment Required: "{"error":"Your balance is low, pls visit the dashboard to top up"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-22T12:25:03.982Z</v>
+        <v>2026-10-22T18:20:01.521Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>402 Payment Required: "{"error":"Your balance is low, pls visit the dashboard to top up"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-22T12:25:07.109Z</v>
+        <v>2026-10-22T18:20:04.704Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>402 Payment Required: "{"error":"Your balance is low, pls visit the dashboard to top up"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-22T18:20:01.521Z</v>
+        <v>2026-10-23T00:19:55.285Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>402 Payment Required: "{"error":"Your balance is low, pls visit the dashboard to top up"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-22T18:20:04.704Z</v>
+        <v>2026-10-23T00:19:58.422Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>402 Payment Required: "{"error":"Your balance is low, pls visit the dashboard to top up"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-23T00:19:55.285Z</v>
+        <v>2026-10-23T06:23:34.581Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>402 Payment Required: "{"error":"Your balance is low, pls visit the dashboard to top up"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-23T00:19:58.422Z</v>
+        <v>2026-10-23T06:23:37.738Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>402 Payment Required: "{"error":"Your balance is low, pls visit the dashboard to top up"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-23T06:23:34.581Z</v>
+        <v>2026-10-23T12:18:16.970Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>402 Payment Required: "{"error":"Your balance is low, pls visit the dashboard to top up"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-23T06:23:37.738Z</v>
+        <v>2026-10-23T12:18:20.097Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -421,10 +421,10 @@
         <v>FAILED</v>
       </c>
       <c r="C2" t="str">
-        <v>402 Payment Required: "{"error":"Your balance is low, pls visit the dashboard to top up"}"</v>
+        <v>Gateway timeout after 25s.</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-23T12:18:16.970Z</v>
+        <v>2026-10-23T18:20:13.970Z</v>
       </c>
     </row>
     <row r="3">
@@ -435,10 +435,10 @@
         <v>FAILED</v>
       </c>
       <c r="C3" t="str">
-        <v>402 Payment Required: "{"error":"Your balance is low, pls visit the dashboard to top up"}"</v>
+        <v>Gateway timeout after 25s.</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-23T12:18:20.097Z</v>
+        <v>2026-10-23T18:20:40.471Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -421,10 +421,10 @@
         <v>FAILED</v>
       </c>
       <c r="C2" t="str">
-        <v>Gateway timeout after 25s.</v>
+        <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-23T18:20:13.970Z</v>
+        <v>2026-10-24T00:21:05.207Z</v>
       </c>
     </row>
     <row r="3">
@@ -435,10 +435,10 @@
         <v>FAILED</v>
       </c>
       <c r="C3" t="str">
-        <v>Gateway timeout after 25s.</v>
+        <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-23T18:20:40.471Z</v>
+        <v>2026-10-24T00:21:09.452Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-24T00:21:05.207Z</v>
+        <v>2026-10-24T06:19:53.727Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-24T00:21:09.452Z</v>
+        <v>2026-10-24T06:19:57.330Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-24T06:19:53.727Z</v>
+        <v>2026-10-24T12:18:16.547Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-24T06:19:57.330Z</v>
+        <v>2026-10-24T12:18:20.218Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -421,10 +421,10 @@
         <v>FAILED</v>
       </c>
       <c r="C2" t="str">
-        <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
+        <v>424 Failed Dependency: "{"error":"Service not Reachable"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-24T12:18:16.547Z</v>
+        <v>2026-10-24T18:14:23.203Z</v>
       </c>
     </row>
     <row r="3">
@@ -435,10 +435,10 @@
         <v>FAILED</v>
       </c>
       <c r="C3" t="str">
-        <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
+        <v>424 Failed Dependency: "{"error":"Service not Reachable"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-24T12:18:20.218Z</v>
+        <v>2026-10-24T18:14:29.901Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>424 Failed Dependency: "{"error":"Service not Reachable"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-24T18:14:23.203Z</v>
+        <v>2026-10-25T00:14:43.775Z</v>
       </c>
     </row>
     <row r="3">
@@ -435,10 +435,10 @@
         <v>FAILED</v>
       </c>
       <c r="C3" t="str">
-        <v>424 Failed Dependency: "{"error":"Service not Reachable"}"</v>
+        <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-24T18:14:29.901Z</v>
+        <v>2026-10-25T00:14:54.392Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -421,10 +421,10 @@
         <v>FAILED</v>
       </c>
       <c r="C2" t="str">
-        <v>424 Failed Dependency: "{"error":"Service not Reachable"}"</v>
+        <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-25T00:14:43.775Z</v>
+        <v>2026-10-25T06:20:41.054Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-25T00:14:54.392Z</v>
+        <v>2026-10-25T06:20:45.229Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-25T06:20:41.054Z</v>
+        <v>2026-10-25T12:18:07.852Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-25T06:20:45.229Z</v>
+        <v>2026-10-25T12:18:11.435Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-25T12:18:07.852Z</v>
+        <v>2026-10-25T18:15:41.848Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-25T12:18:11.435Z</v>
+        <v>2026-10-25T18:15:45.422Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-25T18:15:41.848Z</v>
+        <v>2026-10-26T00:20:05.355Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-25T18:15:45.422Z</v>
+        <v>2026-10-26T00:20:09.004Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-26T00:20:05.355Z</v>
+        <v>2026-10-26T06:27:20.158Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-26T00:20:09.004Z</v>
+        <v>2026-10-26T06:27:23.781Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-26T06:27:20.158Z</v>
+        <v>2026-10-26T14:18:31.200Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-26T06:27:23.781Z</v>
+        <v>2026-10-26T14:18:34.687Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-26T14:18:31.200Z</v>
+        <v>2026-10-26T18:29:01.464Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-26T14:18:34.687Z</v>
+        <v>2026-10-26T18:29:05.098Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-26T18:29:01.464Z</v>
+        <v>2026-10-27T00:21:05.696Z</v>
       </c>
     </row>
     <row r="3">
@@ -435,10 +435,10 @@
         <v>FAILED</v>
       </c>
       <c r="C3" t="str">
-        <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
+        <v>Gateway timeout after 25s.</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-26T18:29:05.098Z</v>
+        <v>2026-10-27T00:21:32.201Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-27T00:21:05.696Z</v>
+        <v>2026-10-27T06:26:43.934Z</v>
       </c>
     </row>
     <row r="3">
@@ -435,10 +435,10 @@
         <v>FAILED</v>
       </c>
       <c r="C3" t="str">
-        <v>Gateway timeout after 25s.</v>
+        <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-27T00:21:32.201Z</v>
+        <v>2026-10-27T06:26:47.335Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-27T06:26:43.934Z</v>
+        <v>2026-10-27T12:28:21.538Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-27T06:26:47.335Z</v>
+        <v>2026-10-27T12:28:25.000Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-27T12:28:21.538Z</v>
+        <v>2026-10-27T18:30:59.546Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-27T12:28:25.000Z</v>
+        <v>2026-10-27T18:31:03.118Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-27T18:30:59.546Z</v>
+        <v>2026-10-28T00:28:22.259Z</v>
       </c>
     </row>
     <row r="3">
@@ -435,10 +435,10 @@
         <v>FAILED</v>
       </c>
       <c r="C3" t="str">
-        <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
+        <v>424 Failed Dependency: "{"error":"Service not Reachable"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-27T18:31:03.118Z</v>
+        <v>2026-10-28T00:28:39.231Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-28T00:28:22.259Z</v>
+        <v>2026-10-28T06:30:38.527Z</v>
       </c>
     </row>
     <row r="3">
@@ -435,10 +435,10 @@
         <v>FAILED</v>
       </c>
       <c r="C3" t="str">
-        <v>424 Failed Dependency: "{"error":"Service not Reachable"}"</v>
+        <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-28T00:28:39.231Z</v>
+        <v>2026-10-28T06:30:42.456Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-28T06:30:38.527Z</v>
+        <v>2026-10-28T12:31:28.395Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-28T06:30:42.456Z</v>
+        <v>2026-10-28T12:31:33.615Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-28T12:31:28.395Z</v>
+        <v>2026-10-28T18:30:46.954Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-28T12:31:33.615Z</v>
+        <v>2026-10-28T18:30:50.926Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-28T18:30:46.954Z</v>
+        <v>2026-10-29T00:28:17.786Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-28T18:30:50.926Z</v>
+        <v>2026-10-29T00:28:21.259Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-29T00:28:17.786Z</v>
+        <v>2026-10-29T06:33:17.138Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-29T00:28:21.259Z</v>
+        <v>2026-10-29T06:33:20.655Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-29T06:33:17.138Z</v>
+        <v>2026-10-29T12:32:23.517Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-29T06:33:20.655Z</v>
+        <v>2026-10-29T12:32:27.057Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-29T12:32:23.517Z</v>
+        <v>2026-10-29T18:33:07.122Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-29T12:32:27.057Z</v>
+        <v>2026-10-29T18:33:10.656Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-29T18:33:07.122Z</v>
+        <v>2026-10-30T00:29:22.020Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-29T18:33:10.656Z</v>
+        <v>2026-10-30T00:29:25.511Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-30T00:29:22.020Z</v>
+        <v>2026-10-30T06:33:23.582Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-30T00:29:25.511Z</v>
+        <v>2026-10-30T06:33:27.172Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-30T06:33:23.582Z</v>
+        <v>2026-10-30T12:32:05.727Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-30T06:33:27.172Z</v>
+        <v>2026-10-30T12:32:09.279Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-30T12:32:05.727Z</v>
+        <v>2026-10-30T18:29:42.860Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-30T12:32:09.279Z</v>
+        <v>2026-10-30T18:29:46.349Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-30T18:29:42.860Z</v>
+        <v>2026-10-31T00:33:48.720Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-30T18:29:46.349Z</v>
+        <v>2026-10-31T00:33:52.278Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-31T00:33:48.720Z</v>
+        <v>2026-10-31T06:32:38.338Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-31T00:33:52.278Z</v>
+        <v>2026-10-31T06:32:42.230Z</v>
       </c>
     </row>
   </sheetData>

--- a/autobot/results/birs_all_results.xlsx
+++ b/autobot/results/birs_all_results.xlsx
@@ -424,7 +424,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-31T06:32:38.338Z</v>
+        <v>2026-10-31T12:29:25.710Z</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         <v>404 Not Found: "{"error":"NIN Not Found"}"</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-10-31T06:32:42.230Z</v>
+        <v>2026-10-31T12:29:29.606Z</v>
       </c>
     </row>
   </sheetData>
